--- a/data/processed/nnt_lrs/nnt_lrs_with_estimated.xlsx
+++ b/data/processed/nnt_lrs/nnt_lrs_with_estimated.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
         <v>34.4</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -506,7 +506,7 @@
         <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         <v>7.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -606,7 +606,7 @@
         <v>3.979949748426479</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +624,7 @@
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +642,7 @@
         <v>3.594440151122286</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         <v>6.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -678,7 +678,7 @@
         <v>5.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -696,7 +696,7 @@
         <v>5.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -714,7 +714,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         <v>5.8</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">
@@ -750,7 +750,7 @@
         <v>6.3</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
@@ -768,7 +768,7 @@
         <v>2.3</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -786,7 +786,7 @@
         <v>3.039736830714133</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -804,7 +804,7 @@
         <v>3.823610858861032</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -822,7 +822,7 @@
         <v>0.13</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -858,7 +858,7 @@
         <v>0.1833030277982336</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
@@ -876,7 +876,7 @@
         <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +894,7 @@
         <v>0.142828568570857</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -957,7 +957,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
         <v>1.92</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1022,7 +1022,7 @@
         <v>0.89</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -1038,7 +1038,7 @@
         <v>0.23</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         <v>0.59</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -1293,7 +1293,7 @@
         <v>4.9</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
@@ -1309,7 +1309,7 @@
         <v>4.7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -1325,7 +1325,7 @@
         <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7">
@@ -1341,7 +1341,7 @@
         <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8">
@@ -1357,7 +1357,7 @@
         <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1373,7 +1373,7 @@
         <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1405,7 +1405,7 @@
         <v>0.38</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -1421,7 +1421,7 @@
         <v>0.48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -1499,7 +1499,7 @@
         <v>0.08</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>6.039867548216599</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -1581,7 +1581,7 @@
         <v>24.37211521390788</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1599,7 +1599,7 @@
         <v>145.8937969894539</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -1635,7 +1635,7 @@
         <v>0.05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -1653,7 +1653,7 @@
         <v>0.03741657386773942</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>13.4</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1731,7 +1731,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         <v>18.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1809,7 +1809,7 @@
         <v>0.27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1887,7 +1887,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1903,7 +1903,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1919,7 +1919,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -1935,7 +1935,7 @@
         <v>0.23</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
         <v>17.4355957741627</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -2035,7 +2035,7 @@
         <v>6.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2053,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -2071,7 +2071,7 @@
         <v>9.1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         <v>4.2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -2107,7 +2107,7 @@
         <v>4.1</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
@@ -2143,7 +2143,7 @@
         <v>0.42</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -2161,7 +2161,7 @@
         <v>0.84</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2197,7 @@
         <v>0.6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -2233,7 +2233,7 @@
         <v>0.52</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
         <v>6.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -2315,7 +2315,7 @@
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2333,7 +2333,7 @@
         <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -2351,7 +2351,7 @@
         <v>2.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -2369,7 +2369,7 @@
         <v>2.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2387,7 +2387,7 @@
         <v>2.1</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -2405,7 +2405,7 @@
         <v>2.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2423,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11">
@@ -2441,7 +2441,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -2459,7 +2459,7 @@
         <v>1.7</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">
@@ -2477,7 +2477,7 @@
         <v>1.5</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -2495,7 +2495,7 @@
         <v>0.3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -2513,7 +2513,7 @@
         <v>0.3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
@@ -2549,7 +2549,7 @@
         <v>0.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="18">
@@ -2567,7 +2567,7 @@
         <v>0.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19">
@@ -2585,7 +2585,7 @@
         <v>0.6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -2603,7 +2603,7 @@
         <v>0.6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -2621,7 +2621,7 @@
         <v>0.7</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -2639,7 +2639,7 @@
         <v>0.7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
@@ -2657,7 +2657,7 @@
         <v>0.8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -2675,7 +2675,7 @@
         <v>0.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>7.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -2757,7 +2757,7 @@
         <v>6.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2775,7 +2775,7 @@
         <v>5.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2793,7 +2793,7 @@
         <v>5.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -2811,7 +2811,7 @@
         <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2847,7 +2847,7 @@
         <v>2.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2865,7 +2865,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2883,7 +2883,7 @@
         <v>1.8</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -2901,7 +2901,7 @@
         <v>1.7</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2973,7 +2973,7 @@
         <v>0.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2991,7 +2991,7 @@
         <v>0.12</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -3009,7 +3009,7 @@
         <v>0.32</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">
@@ -3027,7 +3027,7 @@
         <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3045,7 +3045,7 @@
         <v>0.47</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -3063,7 +3063,7 @@
         <v>0.65</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -3081,7 +3081,7 @@
         <v>0.79</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -3099,7 +3099,7 @@
         <v>0.8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -3117,7 +3117,7 @@
         <v>0.86</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25">
@@ -3135,7 +3135,7 @@
         <v>0.88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -3153,7 +3153,7 @@
         <v>0.91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -3171,7 +3171,7 @@
         <v>0.95</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28">
@@ -3189,7 +3189,7 @@
         <v>1.08</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -3207,7 +3207,7 @@
         <v>1.1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -3225,7 +3225,7 @@
         <v>1.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3307,7 +3307,7 @@
         <v>7.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -3343,7 +3343,7 @@
         <v>5.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3361,7 +3361,7 @@
         <v>1.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="8">
@@ -3379,7 +3379,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -3397,7 +3397,7 @@
         <v>2.3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -3415,7 +3415,7 @@
         <v>0.39</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -3433,7 +3433,7 @@
         <v>0.48</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -3451,7 +3451,7 @@
         <v>0.54</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -3469,7 +3469,7 @@
         <v>0.7</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="14">
@@ -3487,7 +3487,7 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -3505,7 +3505,7 @@
         <v>0.34</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="16">
@@ -3523,7 +3523,7 @@
         <v>0.63</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
         <v>1.8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3623,7 +3623,7 @@
         <v>1.1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3641,7 @@
         <v>1.9</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3659,7 +3659,7 @@
         <v>0.52</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
@@ -3677,7 +3677,7 @@
         <v>0.58</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -3695,7 +3695,7 @@
         <v>0.78</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
         <v>1.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3795,7 +3795,7 @@
         <v>1.367479433117734</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -3813,7 +3813,7 @@
         <v>1.048808848170152</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -3831,7 +3831,7 @@
         <v>1.588080602488425</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3867,7 +3867,7 @@
         <v>1.534926708347992</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -3885,7 +3885,7 @@
         <v>1.587450786638754</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -3903,7 +3903,7 @@
         <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="12">
@@ -3921,7 +3921,7 @@
         <v>2.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -3939,7 +3939,7 @@
         <v>1.8</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="14">
@@ -3957,7 +3957,7 @@
         <v>1.97484176581315</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
@@ -3975,7 +3975,7 @@
         <v>2.083266665599966</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3993,7 +3993,7 @@
         <v>1.4</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -4011,7 +4011,7 @@
         <v>1.50996688705415</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
@@ -4029,7 +4029,7 @@
         <v>1.816590212458495</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4065,7 +4065,7 @@
         <v>1.173030263889214</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -4101,7 +4101,7 @@
         <v>1.037207790175141</v>
       </c>
       <c r="D22" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -4119,7 +4119,7 @@
         <v>1.167475909815701</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
@@ -4137,7 +4137,7 @@
         <v>1.449137674618944</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -4155,7 +4155,7 @@
         <v>6.3</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4173,7 +4173,7 @@
         <v>2.1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4191,7 +4191,7 @@
         <v>0.75</v>
       </c>
       <c r="D27" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4209,7 +4209,7 @@
         <v>0.16</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4227,7 +4227,7 @@
         <v>0.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
         <v>0.5744562646538028</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -4263,7 +4263,7 @@
         <v>0.565685424949238</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
@@ -4281,7 +4281,7 @@
         <v>0.686804193347711</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
@@ -4299,7 +4299,7 @@
         <v>0.7778174593052023</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -4317,7 +4317,7 @@
         <v>0.812403840463596</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
@@ -4371,7 +4371,7 @@
         <v>0.93</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4389,7 +4389,7 @@
         <v>1.074988372030135</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -4407,7 +4407,7 @@
         <v>0.5037856687123999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="40">
@@ -4425,7 +4425,7 @@
         <v>0.8449852069711044</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
@@ -4443,7 +4443,7 @@
         <v>0.8378544026261365</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42">
@@ -4479,7 +4479,7 @@
         <v>0.6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="44">
@@ -4497,7 +4497,7 @@
         <v>0.63</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -4515,7 +4515,7 @@
         <v>0.7876547467006086</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="46">
@@ -4533,7 +4533,7 @@
         <v>0.72</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
@@ -4587,7 +4587,7 @@
         <v>0.99498743710662</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
@@ -4623,7 +4623,7 @@
         <v>1.1</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         <v>1.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -4723,7 +4723,7 @@
         <v>1.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4741,7 +4741,7 @@
         <v>1.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -4759,7 +4759,7 @@
         <v>0.79</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8">
@@ -4777,7 +4777,7 @@
         <v>0.64</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -4795,7 +4795,7 @@
         <v>0.59</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4813,7 +4813,7 @@
         <v>0.48</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -4831,7 +4831,7 @@
         <v>0.44</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -4849,7 +4849,7 @@
         <v>0.44</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -4867,7 +4867,7 @@
         <v>0.41</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -4885,7 +4885,7 @@
         <v>0.34</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -4903,7 +4903,7 @@
         <v>4.7</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -4921,7 +4921,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -4939,7 +4939,7 @@
         <v>2.9</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -4957,7 +4957,7 @@
         <v>2.6</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -4975,7 +4975,7 @@
         <v>0.65</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -4993,7 +4993,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -5011,7 +5011,7 @@
         <v>6.2</v>
       </c>
       <c r="D21" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -5029,7 +5029,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -5047,7 +5047,7 @@
         <v>4.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -5065,7 +5065,7 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -5083,7 +5083,7 @@
         <v>1.8</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -5101,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -5137,7 +5137,7 @@
         <v>0.45</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29">
@@ -5155,7 +5155,7 @@
         <v>0.35</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
@@ -5173,7 +5173,7 @@
         <v>0.12</v>
       </c>
       <c r="D30" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -5209,7 +5209,7 @@
         <v>0.19</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -5245,7 +5245,7 @@
         <v>0.71</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -5281,7 +5281,7 @@
         <v>0.85</v>
       </c>
       <c r="D36" t="n">
-        <v>1.2</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="37">
@@ -5299,7 +5299,7 @@
         <v>0.88</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
@@ -5317,7 +5317,7 @@
         <v>1.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="39">
@@ -5335,7 +5335,7 @@
         <v>1.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -5353,7 +5353,7 @@
         <v>1.1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="41">
@@ -5371,7 +5371,7 @@
         <v>1.1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42">
@@ -5389,7 +5389,7 @@
         <v>1.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -5407,7 +5407,7 @@
         <v>1.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="44">
@@ -5443,7 +5443,7 @@
         <v>1.2</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="46">
@@ -5461,7 +5461,7 @@
         <v>0.73</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="47">
@@ -5479,7 +5479,7 @@
         <v>0.66</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -5497,7 +5497,7 @@
         <v>0.65</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="49">
@@ -5515,7 +5515,7 @@
         <v>0.93</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
@@ -5533,7 +5533,7 @@
         <v>1.7</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
@@ -5569,7 +5569,7 @@
         <v>0.83</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="53">
@@ -5623,7 +5623,7 @@
         <v>1.1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56">
@@ -5659,7 +5659,7 @@
         <v>1.2</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="58">
@@ -5677,7 +5677,7 @@
         <v>0.28</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
         <v>5.8</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -5823,7 +5823,7 @@
         <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -5859,7 +5859,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5877,7 +5877,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -5895,7 +5895,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -5913,7 +5913,7 @@
         <v>4.1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -5949,7 +5949,7 @@
         <v>0.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -5967,7 +5967,7 @@
         <v>0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -5985,7 +5985,7 @@
         <v>0.11</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -6003,7 +6003,7 @@
         <v>0.16</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -6021,7 +6021,7 @@
         <v>0.52</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -6039,7 +6039,7 @@
         <v>0.82</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
         <v>7.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -6157,7 +6157,7 @@
         <v>6.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -6175,7 +6175,7 @@
         <v>6.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -6193,7 +6193,7 @@
         <v>6.3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -6211,7 +6211,7 @@
         <v>3.7</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -6229,7 +6229,7 @@
         <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -6247,7 +6247,7 @@
         <v>3.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6283,7 +6283,7 @@
         <v>2.2</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -6301,7 +6301,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -6319,7 +6319,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -6337,7 +6337,7 @@
         <v>1.4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -6355,7 +6355,7 @@
         <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -6373,7 +6373,7 @@
         <v>1.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -6409,7 +6409,7 @@
         <v>0.88</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -6427,7 +6427,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
@@ -6445,7 +6445,7 @@
         <v>4.2</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
@@ -6463,7 +6463,7 @@
         <v>2.8</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23">
@@ -6481,7 +6481,7 @@
         <v>2.5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6499,7 +6499,7 @@
         <v>2.5</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25">
@@ -6517,7 +6517,7 @@
         <v>2.1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="26">
@@ -6535,7 +6535,7 @@
         <v>2.1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27">
@@ -6571,7 +6571,7 @@
         <v>0.48</v>
       </c>
       <c r="D28" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -6607,7 +6607,7 @@
         <v>0.34</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -6625,7 +6625,7 @@
         <v>0.36</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
@@ -6643,7 +6643,7 @@
         <v>0.38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
@@ -6679,7 +6679,7 @@
         <v>0.5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="35">
@@ -6715,7 +6715,7 @@
         <v>0.54</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -6751,7 +6751,7 @@
         <v>0.58</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="39">
@@ -6769,7 +6769,7 @@
         <v>0.75</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40">
@@ -6787,7 +6787,7 @@
         <v>0.84</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="41">
@@ -6805,7 +6805,7 @@
         <v>0.88</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="42">
@@ -6823,7 +6823,7 @@
         <v>0.9</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -6841,7 +6841,7 @@
         <v>0.95</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -6877,7 +6877,7 @@
         <v>3.3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="46">
@@ -6913,7 +6913,7 @@
         <v>0.34</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -6931,7 +6931,7 @@
         <v>0.36</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -6949,7 +6949,7 @@
         <v>0.38</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
@@ -6967,7 +6967,7 @@
         <v>0.46</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
@@ -6985,7 +6985,7 @@
         <v>0.48</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="52">
@@ -7003,7 +7003,7 @@
         <v>0.5</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="53">
@@ -7075,7 +7075,7 @@
         <v>0.57</v>
       </c>
       <c r="D56" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57">
@@ -7093,7 +7093,7 @@
         <v>0.58</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="58">
@@ -7129,7 +7129,7 @@
         <v>0.66</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60">
@@ -7147,7 +7147,7 @@
         <v>0.67</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="61">
@@ -7165,7 +7165,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="62">
@@ -7183,7 +7183,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63">
@@ -7201,7 +7201,7 @@
         <v>0.75</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="64">
@@ -7219,7 +7219,7 @@
         <v>0.84</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="65">
@@ -7237,7 +7237,7 @@
         <v>0.88</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="66">
@@ -7255,7 +7255,7 @@
         <v>0.9</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="67">
@@ -7273,7 +7273,7 @@
         <v>0.95</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68">
@@ -7291,7 +7291,7 @@
         <v>0.97</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="69">
@@ -7309,7 +7309,7 @@
         <v>1.3</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
@@ -7327,7 +7327,7 @@
         <v>3.3</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
         <v>4.6</v>
       </c>
       <c r="D3" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -7409,7 +7409,7 @@
         <v>4.3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5">
@@ -7427,7 +7427,7 @@
         <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -7445,7 +7445,7 @@
         <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7463,7 +7463,7 @@
         <v>2.7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -7481,7 +7481,7 @@
         <v>2.6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -7499,7 +7499,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7517,7 +7517,7 @@
         <v>1.9</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -7535,7 +7535,7 @@
         <v>1.6</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -7553,7 +7553,7 @@
         <v>1.6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">
@@ -7571,7 +7571,7 @@
         <v>1.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7589,7 +7589,7 @@
         <v>1.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -7607,7 +7607,7 @@
         <v>1.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -7625,7 +7625,7 @@
         <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -7643,7 +7643,7 @@
         <v>1.2</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
@@ -7679,7 +7679,7 @@
         <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -7697,7 +7697,7 @@
         <v>1.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="21">
@@ -7715,7 +7715,7 @@
         <v>1.1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="22">
@@ -7733,7 +7733,7 @@
         <v>1.1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -7751,7 +7751,7 @@
         <v>1.1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -7769,7 +7769,7 @@
         <v>1.1</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25">
@@ -7787,7 +7787,7 @@
         <v>1.1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -7805,7 +7805,7 @@
         <v>0.97</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
@@ -7823,7 +7823,7 @@
         <v>0.93</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="28">
@@ -7841,7 +7841,7 @@
         <v>0.85</v>
       </c>
       <c r="D28" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -7859,7 +7859,7 @@
         <v>0.83</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -7877,7 +7877,7 @@
         <v>0.71</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31">
@@ -7895,7 +7895,7 @@
         <v>0.41</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
@@ -7913,7 +7913,7 @@
         <v>0.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33">
@@ -7949,7 +7949,7 @@
         <v>0.53</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -7967,7 +7967,7 @@
         <v>0.67</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="36">
@@ -7985,7 +7985,7 @@
         <v>0.7</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="37">
@@ -8003,7 +8003,7 @@
         <v>0.71</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="38">
@@ -8039,7 +8039,7 @@
         <v>0.79</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="40">
@@ -8129,7 +8129,7 @@
         <v>0.87</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="45">
@@ -8147,7 +8147,7 @@
         <v>0.89</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46">
@@ -8165,7 +8165,7 @@
         <v>0.92</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
@@ -8183,7 +8183,7 @@
         <v>0.93</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -8201,7 +8201,7 @@
         <v>0.93</v>
       </c>
       <c r="D48" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -8219,7 +8219,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -8237,7 +8237,7 @@
         <v>0.95</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="51">
@@ -8255,7 +8255,7 @@
         <v>0.97</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="52">
@@ -8273,7 +8273,7 @@
         <v>0.99</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="53">
@@ -8345,7 +8345,7 @@
         <v>1.1</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57">
@@ -8363,7 +8363,7 @@
         <v>1.1</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="58">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
         <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -8463,7 +8463,7 @@
         <v>2.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -8481,7 +8481,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -8499,7 +8499,7 @@
         <v>1.6</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -8517,7 +8517,7 @@
         <v>1.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -8535,7 +8535,7 @@
         <v>1.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -8553,7 +8553,7 @@
         <v>1.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -8571,7 +8571,7 @@
         <v>1.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -8607,7 +8607,7 @@
         <v>1.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
@@ -8625,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
@@ -8643,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -8661,7 +8661,7 @@
         <v>0.97</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -8679,7 +8679,7 @@
         <v>2.6</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
@@ -8697,7 +8697,7 @@
         <v>2.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8715,7 +8715,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8733,7 +8733,7 @@
         <v>1.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -8751,7 +8751,7 @@
         <v>1.643167672515498</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -8769,7 +8769,7 @@
         <v>1.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -8823,7 +8823,7 @@
         <v>1.3</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -8841,7 +8841,7 @@
         <v>1.349073756323204</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
@@ -8859,7 +8859,7 @@
         <v>1.2</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -8877,7 +8877,7 @@
         <v>1.1</v>
       </c>
       <c r="D27" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -8895,7 +8895,7 @@
         <v>1.1</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -8913,7 +8913,7 @@
         <v>2.387467277262664</v>
       </c>
       <c r="D29" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="30">
@@ -8949,7 +8949,7 @@
         <v>1.005982107196743</v>
       </c>
       <c r="D31" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="32">
@@ -8967,7 +8967,7 @@
         <v>0.71</v>
       </c>
       <c r="D32" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -8985,7 +8985,7 @@
         <v>0.55</v>
       </c>
       <c r="D33" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="34">
@@ -9003,7 +9003,7 @@
         <v>0.4620606020859169</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -9021,7 +9021,7 @@
         <v>3.9</v>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="36">
@@ -9039,7 +9039,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37">
@@ -9057,7 +9057,7 @@
         <v>1.9</v>
       </c>
       <c r="D37" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="38">
@@ -9075,7 +9075,7 @@
         <v>1.3</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="39">
@@ -9093,7 +9093,7 @@
         <v>0.28</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -9111,7 +9111,7 @@
         <v>5.3</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="41">
@@ -9129,7 +9129,7 @@
         <v>3.6</v>
       </c>
       <c r="D41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -9147,7 +9147,7 @@
         <v>1.8</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="43">
@@ -9165,7 +9165,7 @@
         <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -9183,7 +9183,7 @@
         <v>6.8</v>
       </c>
       <c r="D44" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -9201,7 +9201,7 @@
         <v>2.4</v>
       </c>
       <c r="D45" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="46">
@@ -9219,7 +9219,7 @@
         <v>2.4</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="47">
@@ -9237,7 +9237,7 @@
         <v>2.8</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="48">
@@ -9255,7 +9255,7 @@
         <v>0.79</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="49">
@@ -9273,7 +9273,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -9291,7 +9291,7 @@
         <v>0.2</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
@@ -9309,7 +9309,7 @@
         <v>0.31</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="52">
@@ -9327,7 +9327,7 @@
         <v>0.24</v>
       </c>
       <c r="D52" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="53">
@@ -9345,7 +9345,7 @@
         <v>0.7</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="54">
@@ -9363,7 +9363,7 @@
         <v>0.75</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="55">
@@ -9381,7 +9381,7 @@
         <v>0.78</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56">
@@ -9399,7 +9399,7 @@
         <v>0.85</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="57">
@@ -9417,7 +9417,7 @@
         <v>0.88</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="58">
@@ -9435,7 +9435,7 @@
         <v>0.9</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="59">
@@ -9453,7 +9453,7 @@
         <v>0.92</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="60">
@@ -9489,7 +9489,7 @@
         <v>0.96</v>
       </c>
       <c r="D61" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="62">
@@ -9507,7 +9507,7 @@
         <v>0.97</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="63">
@@ -9525,7 +9525,7 @@
         <v>0.99</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="64">
@@ -9543,7 +9543,7 @@
         <v>0.99</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="65">
@@ -9561,7 +9561,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="66">
@@ -9579,7 +9579,7 @@
         <v>0.52</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="67">
@@ -9597,7 +9597,7 @@
         <v>0.7401351227985333</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="68">
@@ -9633,7 +9633,7 @@
         <v>0.75</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
@@ -9651,7 +9651,7 @@
         <v>0.8378544026261365</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="71">
@@ -9669,7 +9669,7 @@
         <v>0.8</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="72">
@@ -9687,7 +9687,7 @@
         <v>0.84</v>
       </c>
       <c r="D72" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73">
@@ -9705,7 +9705,7 @@
         <v>0.88</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="74">
@@ -9723,7 +9723,7 @@
         <v>0.89</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="75">
@@ -9741,7 +9741,7 @@
         <v>0.9</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="76">
@@ -9759,7 +9759,7 @@
         <v>0.91</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="77">
@@ -9777,7 +9777,7 @@
         <v>0.919945650568554</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="78">
@@ -9795,7 +9795,7 @@
         <v>0.93</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="79">
@@ -9813,7 +9813,7 @@
         <v>0.9848857801796105</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80">
@@ -9849,7 +9849,7 @@
         <v>0.99</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="82">
@@ -9867,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="83">
@@ -9903,7 +9903,7 @@
         <v>1.148912529307606</v>
       </c>
       <c r="D84" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="85">
@@ -9921,7 +9921,7 @@
         <v>0.95</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="86">
@@ -9939,7 +9939,7 @@
         <v>0.95</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87">
@@ -9957,7 +9957,7 @@
         <v>0.98</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="88">
@@ -9975,7 +9975,7 @@
         <v>0.99</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="89">
@@ -9993,7 +9993,7 @@
         <v>1.2</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="90">
@@ -10047,7 +10047,7 @@
         <v>0.89</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
         <v>21.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -10129,7 +10129,7 @@
         <v>7.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
@@ -10147,7 +10147,7 @@
         <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -10165,7 +10165,7 @@
         <v>2.7</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -10184,7 +10184,7 @@
         <v>2.4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -10203,7 +10203,7 @@
         <v>1.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -10221,7 +10221,7 @@
         <v>1.6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -10239,7 +10239,7 @@
         <v>1.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -10258,7 +10258,7 @@
         <v>1.5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -10276,7 +10276,7 @@
         <v>1.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -10294,7 +10294,7 @@
         <v>1.4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14">
@@ -10312,7 +10312,7 @@
         <v>1.3</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
@@ -10330,7 +10330,7 @@
         <v>1.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -10349,7 +10349,7 @@
         <v>1.3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -10387,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -10405,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -10423,7 +10423,7 @@
         <v>0.1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -10441,7 +10441,7 @@
         <v>0.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22">
@@ -10460,7 +10460,7 @@
         <v>0.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -10478,7 +10478,7 @@
         <v>0.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -10533,7 +10533,7 @@
         <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -10552,7 +10552,7 @@
         <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -10589,7 +10589,7 @@
         <v>0.7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30">
@@ -10607,7 +10607,7 @@
         <v>0.7</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -10625,7 +10625,7 @@
         <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32">
@@ -10643,7 +10643,7 @@
         <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -10661,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -10717,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         <v>10.8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -10799,7 +10799,7 @@
         <v>7.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -10817,7 +10817,7 @@
         <v>2.6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -10835,7 +10835,7 @@
         <v>1.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -10853,7 +10853,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -10871,7 +10871,7 @@
         <v>4.9</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9">
@@ -10889,7 +10889,7 @@
         <v>2.7</v>
       </c>
       <c r="D9" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -10907,7 +10907,7 @@
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -10925,7 +10925,7 @@
         <v>3.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -10961,7 +10961,7 @@
         <v>0.4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -11015,7 +11015,7 @@
         <v>0.63</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -11033,7 +11033,7 @@
         <v>0.87</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="18">
@@ -11051,7 +11051,7 @@
         <v>1.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="19">
@@ -11087,7 +11087,7 @@
         <v>0.84</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
         <v>1.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -11187,7 +11187,7 @@
         <v>1.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -11223,7 +11223,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -11241,7 +11241,7 @@
         <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11303,7 @@
         <v>6.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -11319,7 +11319,7 @@
         <v>6.4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -11335,7 +11335,7 @@
         <v>5.6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -11367,7 +11367,7 @@
         <v>7.4</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -11383,7 +11383,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -11431,7 +11431,7 @@
         <v>0.53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -11447,7 +11447,7 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -11463,7 +11463,7 @@
         <v>0.16</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -11479,7 +11479,7 @@
         <v>0.21</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
         <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -11561,7 +11561,7 @@
         <v>2.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
@@ -11579,7 +11579,7 @@
         <v>2.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -11597,7 +11597,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -11615,7 +11615,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11633,7 +11633,7 @@
         <v>1.7</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -11651,7 +11651,7 @@
         <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -11669,7 +11669,7 @@
         <v>1.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -11687,7 +11687,7 @@
         <v>1.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -11705,7 +11705,7 @@
         <v>0.93</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -11723,7 +11723,7 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -11741,7 +11741,7 @@
         <v>4.3</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -11759,7 +11759,7 @@
         <v>2.7</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -11777,7 +11777,7 @@
         <v>2.6</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -11795,7 +11795,7 @@
         <v>2.4</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -11813,7 +11813,7 @@
         <v>1.6</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -11831,7 +11831,7 @@
         <v>0.85</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20">
@@ -11849,7 +11849,7 @@
         <v>9.9</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -11867,7 +11867,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
@@ -11885,7 +11885,7 @@
         <v>7.1</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -11903,7 +11903,7 @@
         <v>4.6</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="24">
@@ -11921,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25">
@@ -11939,7 +11939,7 @@
         <v>0.53</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26">
@@ -11957,7 +11957,7 @@
         <v>0.11</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -11993,7 +11993,7 @@
         <v>4.6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
@@ -12011,7 +12011,7 @@
         <v>3.1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -12029,7 +12029,7 @@
         <v>4.1</v>
       </c>
       <c r="D30" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="31">
@@ -12047,7 +12047,7 @@
         <v>0.67</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32">
@@ -12083,7 +12083,7 @@
         <v>0.84</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -12101,7 +12101,7 @@
         <v>0.84</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35">
@@ -12119,7 +12119,7 @@
         <v>0.85</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -12137,7 +12137,7 @@
         <v>0.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
@@ -12155,7 +12155,7 @@
         <v>0.92</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -12173,7 +12173,7 @@
         <v>0.68</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -12191,7 +12191,7 @@
         <v>0.79</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -12209,7 +12209,7 @@
         <v>1.1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -12227,7 +12227,7 @@
         <v>0.39</v>
       </c>
       <c r="D41" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
@@ -12245,7 +12245,7 @@
         <v>0.41</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -12263,7 +12263,7 @@
         <v>0.65</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="44">
@@ -12281,7 +12281,7 @@
         <v>0.83</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -12299,7 +12299,7 @@
         <v>0.91</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46">
@@ -12317,7 +12317,7 @@
         <v>0.99</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="47">
@@ -12335,7 +12335,7 @@
         <v>1.2</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -12353,7 +12353,7 @@
         <v>0.65</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49">
@@ -12389,7 +12389,7 @@
         <v>0.68</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51">
@@ -12407,7 +12407,7 @@
         <v>0.78</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="52">
@@ -12425,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="53">
@@ -12443,7 +12443,7 @@
         <v>1.1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -12461,7 +12461,7 @@
         <v>1.7</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="55">
@@ -12479,7 +12479,7 @@
         <v>0.73</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="56">
@@ -12497,7 +12497,7 @@
         <v>0.83</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
@@ -12515,7 +12515,7 @@
         <v>0.84</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -12533,7 +12533,7 @@
         <v>0.09</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>5.8</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -12615,7 +12615,7 @@
         <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -12633,7 +12633,7 @@
         <v>1.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -12651,7 +12651,7 @@
         <v>1.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -12669,7 +12669,7 @@
         <v>1.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8">
@@ -12687,7 +12687,7 @@
         <v>1.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -12705,7 +12705,7 @@
         <v>0.84</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -12723,7 +12723,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -12741,7 +12741,7 @@
         <v>2.6</v>
       </c>
       <c r="D11" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
@@ -12759,7 +12759,7 @@
         <v>2.2</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
@@ -12777,7 +12777,7 @@
         <v>2.1</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -12795,7 +12795,7 @@
         <v>1.3</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -12813,7 +12813,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -12849,7 +12849,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="18">
@@ -12885,7 +12885,7 @@
         <v>5.1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -12903,7 +12903,7 @@
         <v>2.8</v>
       </c>
       <c r="D20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -12939,7 +12939,7 @@
         <v>2.3</v>
       </c>
       <c r="D22" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="23">
@@ -12957,7 +12957,7 @@
         <v>2.1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24">
@@ -12993,7 +12993,7 @@
         <v>1.6</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -13011,7 +13011,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
@@ -13029,7 +13029,7 @@
         <v>0.52</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28">
@@ -13047,7 +13047,7 @@
         <v>4.4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -13083,7 +13083,7 @@
         <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -13119,7 +13119,7 @@
         <v>3.3</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -13137,7 +13137,7 @@
         <v>3.2</v>
       </c>
       <c r="D33" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="34">
@@ -13155,7 +13155,7 @@
         <v>3.1</v>
       </c>
       <c r="D34" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="35">
@@ -13173,7 +13173,7 @@
         <v>0.5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -13191,7 +13191,7 @@
         <v>0.38</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
@@ -13209,7 +13209,7 @@
         <v>3.8</v>
       </c>
       <c r="D37" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -13227,7 +13227,7 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -13245,7 +13245,7 @@
         <v>2.2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -13263,7 +13263,7 @@
         <v>1.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="41">
@@ -13281,7 +13281,7 @@
         <v>1.7</v>
       </c>
       <c r="D41" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="42">
@@ -13299,7 +13299,7 @@
         <v>4.6</v>
       </c>
       <c r="D42" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="43">
@@ -13317,7 +13317,7 @@
         <v>3.7</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="44">
@@ -13335,7 +13335,7 @@
         <v>3.1</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -13353,7 +13353,7 @@
         <v>3.1</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="46">
@@ -13389,7 +13389,7 @@
         <v>1.7</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="48">
@@ -13407,7 +13407,7 @@
         <v>0.45</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="49">
@@ -13443,7 +13443,7 @@
         <v>0.68</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51">
@@ -13461,7 +13461,7 @@
         <v>0.71</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52">
@@ -13479,7 +13479,7 @@
         <v>0.89</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="53">
@@ -13497,7 +13497,7 @@
         <v>0.86</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="54">
@@ -13515,7 +13515,7 @@
         <v>1.4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="55">
@@ -13533,7 +13533,7 @@
         <v>1.1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56">
@@ -13551,7 +13551,7 @@
         <v>0.48</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
@@ -13569,7 +13569,7 @@
         <v>0.64</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="58">
@@ -13587,7 +13587,7 @@
         <v>0.65</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="59">
@@ -13641,7 +13641,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="62">
@@ -13677,7 +13677,7 @@
         <v>0.51</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="64">
@@ -13695,7 +13695,7 @@
         <v>0.64</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="65">
@@ -13749,7 +13749,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="68">
@@ -13785,7 +13785,7 @@
         <v>0.97</v>
       </c>
       <c r="D69" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="70">
@@ -13803,7 +13803,7 @@
         <v>0.98</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="71">
@@ -13821,7 +13821,7 @@
         <v>0.99</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="72">
@@ -13839,7 +13839,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="73">
@@ -13857,7 +13857,7 @@
         <v>1.3</v>
       </c>
       <c r="D73" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="74">
@@ -13875,7 +13875,7 @@
         <v>0.45</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="75">
@@ -13911,7 +13911,7 @@
         <v>0.38</v>
       </c>
       <c r="D76" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="77">
@@ -13929,7 +13929,7 @@
         <v>0.48</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="78">
@@ -13965,7 +13965,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="80">
@@ -13983,7 +13983,7 @@
         <v>0.95</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
@@ -14001,7 +14001,7 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="82">
@@ -14019,7 +14019,7 @@
         <v>1.1</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83">
@@ -14037,7 +14037,7 @@
         <v>0.64</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="84">
@@ -14055,7 +14055,7 @@
         <v>0.79</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="85">
@@ -14091,7 +14091,7 @@
         <v>0.98</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="87">
@@ -14109,7 +14109,7 @@
         <v>0.95</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="88">
@@ -14127,7 +14127,7 @@
         <v>0.06</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="89">
@@ -14199,7 +14199,7 @@
         <v>0.11</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="93">
@@ -14217,7 +14217,7 @@
         <v>0.14</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="94">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lr_gpt-4o-mini-2024-07-18</t>
+          <t>lr_gpt-4.1-nano-2025-04-14</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
         <v>5.3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -14313,7 +14313,7 @@
         <v>7.9</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
